--- a/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
+++ b/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
+++ b/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
@@ -1,163 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utilisateur/kDrive/Claude_Travail/livrables/documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C42EBF84-BD26-4042-8D24-FFD698DDA3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="500" windowWidth="36820" windowHeight="21180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4140" yWindow="500" windowWidth="36820" windowHeight="21180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
-  <si>
-    <t>Tes 9 jobs</t>
-  </si>
-  <si>
-    <t>Jour</t>
-  </si>
-  <si>
-    <t>Heure</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Numéro de la dernière leçon</t>
-  </si>
-  <si>
-    <t>Dimanche</t>
-  </si>
-  <si>
-    <t>8h03</t>
-  </si>
-  <si>
-    <t>imac-veille</t>
-  </si>
-  <si>
-    <t>Veille</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>11h03</t>
-  </si>
-  <si>
-    <t>controle-livrables</t>
-  </si>
-  <si>
-    <t>Contrôle qualité</t>
-  </si>
-  <si>
-    <t>Lundi</t>
-  </si>
-  <si>
-    <t>8h30</t>
-  </si>
-  <si>
-    <t>rbpp-pipeline</t>
-  </si>
-  <si>
-    <t>Veille HAS + quiz + infographies</t>
-  </si>
-  <si>
-    <t>Mardi</t>
-  </si>
-  <si>
-    <t>9h03</t>
-  </si>
-  <si>
-    <t>hypnose-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 20</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Mercredi</t>
-  </si>
-  <si>
-    <t>serafin-ph-veille</t>
-  </si>
-  <si>
-    <t>Jeudi</t>
-  </si>
-  <si>
-    <t>stoicisme-lecon</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>9h33</t>
-  </si>
-  <si>
-    <t>astrologie-karmique-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 12</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Vendredi</t>
-  </si>
-  <si>
-    <t>ai-act-veille</t>
-  </si>
-  <si>
-    <t>Veille — réglementaire</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>placement-financier-lecon</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -197,23 +75,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -501,185 +438,287 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col width="13.83203125" customWidth="1" min="1" max="1"/>
+    <col width="40.6640625" customWidth="1" min="3" max="3"/>
+    <col width="30.33203125" customWidth="1" min="4" max="4"/>
+    <col width="26.83203125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tes 9 jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Numéro de la dernière leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>imac-veille</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>11h03</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>controle-livrables</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>8h30</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>rbpp-pipeline</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Veille HAS + quiz + infographies</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>hypnose-lecon</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>serafin-ph-veille</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>stoicisme-lecon</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>9h33</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>astrologie-karmique-lecon</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>ai-act-veille</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Veille — réglementaire</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>placement-financier-lecon</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
+++ b/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
@@ -1,169 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utilisateur/kDrive/Claude_Travail/livrables/documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A556DEAA-25A8-E54F-AA8F-D97B953F2C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="500" windowWidth="36820" windowHeight="21180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4140" yWindow="500" windowWidth="36820" windowHeight="21180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
-  <si>
-    <t>Tes 9 jobs</t>
-  </si>
-  <si>
-    <t>Jour</t>
-  </si>
-  <si>
-    <t>Heure</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Numéro de la dernière leçon</t>
-  </si>
-  <si>
-    <t>Dimanche</t>
-  </si>
-  <si>
-    <t>8h03</t>
-  </si>
-  <si>
-    <t>imac-veille</t>
-  </si>
-  <si>
-    <t>Veille</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>11h03</t>
-  </si>
-  <si>
-    <t>controle-livrables</t>
-  </si>
-  <si>
-    <t>Contrôle qualité</t>
-  </si>
-  <si>
-    <t>Lundi</t>
-  </si>
-  <si>
-    <t>8h30</t>
-  </si>
-  <si>
-    <t>rbpp-pipeline</t>
-  </si>
-  <si>
-    <t>Veille HAS + quiz + infographies</t>
-  </si>
-  <si>
-    <t>Mardi</t>
-  </si>
-  <si>
-    <t>9h03</t>
-  </si>
-  <si>
-    <t>hypnose-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 20</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Mercredi</t>
-  </si>
-  <si>
-    <t>serafin-ph-veille</t>
-  </si>
-  <si>
-    <t>Jeudi</t>
-  </si>
-  <si>
-    <t>stoicisme-lecon</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>9h33</t>
-  </si>
-  <si>
-    <t>astrologie-karmique-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 12</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Vendredi</t>
-  </si>
-  <si>
-    <t>ai-act-veille</t>
-  </si>
-  <si>
-    <t>Veille — réglementaire</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>placement-financier-lecon</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="20"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="20"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -203,24 +82,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -508,190 +446,292 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="38.83203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="45" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="41.83203125" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tes 9 jobs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Numéro de la dernière leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>imac-veille</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>11h03</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>controle-livrables</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>8h30</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>rbpp-pipeline</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Veille HAS + quiz + infographies</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>hypnose-lecon</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>serafin-ph-veille</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>stoicisme-lecon</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>9h33</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>astrologie-karmique-lecon</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ai-act-veille</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Veille — réglementaire</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>placement-financier-lecon</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
+++ b/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
+++ b/livrables/documents/2026-10-15_Les 9 Jobs.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
